--- a/output/pdf_financials_xlsx/BM.xlsx
+++ b/output/pdf_financials_xlsx/BM.xlsx
@@ -5637,52 +5637,52 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.5152</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.617178</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.758971</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.844569</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.844569</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.844569</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.899536</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.900747</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.900747</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.900747</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.900747</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.900747</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.900747</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.358406</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.358406</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.358406</v>
       </c>
     </row>
     <row r="93">
@@ -9430,7 +9430,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10106,7 +10110,11 @@
           <t>Share-based payment reserve 6</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -11406,7 +11414,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12144,7 +12156,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -15758,7 +15774,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -16424,7 +16444,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -17950,7 +17974,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -19266,7 +19294,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E119" s="5" t="n">
         <v>3.5152</v>
       </c>

--- a/output/pdf_financials_xlsx/BM.xlsx
+++ b/output/pdf_financials_xlsx/BM.xlsx
@@ -1020,49 +1020,49 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.027769</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000675</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003054</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.02344</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000435</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000404</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000376</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000361</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000299</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000181</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.009604</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.009604</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.029983</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.030427</v>
       </c>
     </row>
     <row r="13">
@@ -1943,49 +1943,49 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.049995</v>
+        <v>-1.077764</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.158469</v>
+        <v>-1.159144</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.148704</v>
+        <v>-1.151758</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.316648</v>
+        <v>-0.340088</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-15.901713</v>
+        <v>-15.902148</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.309569</v>
+        <v>-0.310069</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.190381</v>
+        <v>-0.190785</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.227329</v>
+        <v>-0.227705</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.242808</v>
+        <v>-0.243169</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.185426</v>
+        <v>-0.185725</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.217124</v>
+        <v>-0.217305</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.266801</v>
+        <v>-0.276405</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.235576</v>
+        <v>-0.24518</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.023512</v>
+        <v>-0.053495</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.008973999999999999</v>
+        <v>-0.039401</v>
       </c>
     </row>
     <row r="28">
@@ -2057,49 +2057,49 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.9562889999999999</v>
+        <v>-0.984058</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.105426</v>
+        <v>-1.106101</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.113753</v>
+        <v>-1.116807</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.295524</v>
+        <v>-0.318964</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-15.887439</v>
+        <v>-15.887874</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.306325</v>
+        <v>-0.306825</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.188784</v>
+        <v>-0.189188</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.226104</v>
+        <v>-0.22648</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.241865</v>
+        <v>-0.242226</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.184697</v>
+        <v>-0.184996</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.216559</v>
+        <v>-0.21674</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.266362</v>
+        <v>-0.275966</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.233966</v>
+        <v>-0.24357</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.023512</v>
+        <v>-0.053495</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.008973999999999999</v>
+        <v>-0.039401</v>
       </c>
     </row>
     <row r="30">
@@ -2365,25 +2365,25 @@
         <v>0.044613</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.082542</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.08107</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.052656</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.009504</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.014059</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.01128</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000328</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.739789</v>
@@ -2475,25 +2475,25 @@
         <v>0.044696</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>8.3e-05</v>
+        <v>0.082625</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>8.3e-05</v>
+        <v>0.081153</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>8.3e-05</v>
+        <v>0.052739</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>8.3e-05</v>
+        <v>0.009587</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>8.3e-05</v>
+        <v>0.014142</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>8.3e-05</v>
+        <v>0.011363</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>8.3e-05</v>
+        <v>0.000411</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.739789</v>
@@ -3135,25 +3135,25 @@
         <v>0.015692</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.095003</v>
+        <v>0.012461</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.094781</v>
+        <v>0.013711</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.060887</v>
+        <v>0.008231</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.01965</v>
+        <v>0.010146</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.022387</v>
+        <v>0.008328</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.016795</v>
+        <v>0.005515</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.001953</v>
+        <v>1.001625</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.000875</v>
@@ -8758,7 +8758,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -10210,7 +10214,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10486,7 +10490,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -15146,7 +15154,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -17394,7 +17406,11 @@
           <t>Reclamation deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -18914,7 +18930,11 @@
           <t>Reclamation deposits (note 7)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>0.0425</v>
       </c>
@@ -23180,7 +23200,11 @@
           <t>Write-off reclamation deposit</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -29438,7 +29462,11 @@
           <t>Increase in reclamation deposit</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -30780,7 +30808,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -32012,7 +32040,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -34198,7 +34226,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -34466,7 +34494,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -35960,7 +35988,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -36620,7 +36648,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -40610,7 +40638,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
